--- a/out/MLP-Mamba1_repeat_3_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.331760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9011568254762614</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001440624600977171</v>
+        <v>-0.0001380188882052898</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1655000969062406</v>
+        <v>-0.158557193576799</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9011568254762614</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.331760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1586952124650043</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1657682518138685</v>
+        <v>-0.1588147153856369</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4462079236830044</v>
+        <v>0.4297052869269928</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7275048455840717</v>
+        <v>0.7014209083545171</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03179222087841815</v>
+        <v>0.03061641147437863</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.931760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.34416515618997</v>
+        <v>0.3322591499309603</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05575285145953988</v>
+        <v>0.05369075406825549</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.931760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4238679552313215</v>
+        <v>0.4090140291856351</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06773313016383531</v>
+        <v>0.06522761357866035</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5035760591860627</v>
+        <v>0.4857740177196856</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0179237182952341</v>
+        <v>0.01726102585669921</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4716042187207353</v>
+        <v>0.4549845530932704</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009957424659006186</v>
+        <v>0.009589084597962469</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.331760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4735784377646129</v>
+        <v>0.4568855592139345</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02092243924636031</v>
+        <v>0.02014736287716608</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.931760215741336</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5054782394943614</v>
+        <v>0.4876048017157139</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008216978835471123</v>
+        <v>0.007912999355768183</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.500971457269542</v>
+        <v>0.4832644574550171</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005849429848778323</v>
+        <v>0.005633812956881657</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5044516383535103</v>
+        <v>0.4866157848362827</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002299341364440974</v>
+        <v>0.002213794218913702</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5031959673674898</v>
+        <v>0.4854065305388712</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001303659778791039</v>
+        <v>0.001254334557446736</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5035012441204346</v>
+        <v>0.4857002962685574</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.00049293255380905</v>
+        <v>0.0004753170153488242</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5031835784416129</v>
+        <v>0.4853940463598156</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002284036140042285</v>
+        <v>0.0002195959304568991</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5031470254295733</v>
+        <v>0.4853586812540048</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.057648120152129e-05</v>
+        <v>7.734718002410539e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5030792849977775</v>
+        <v>0.4852932972917885</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.028024483792712e-05</v>
+        <v>1.932627333460911e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.503038856734124</v>
+        <v>0.4852541934631246</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>7.401629543134059e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.066793665939915</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5030338366287889</v>
+        <v>0.4852491741024316</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5030298185844452</v>
+        <v>0.485245119309596</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5030273839142544</v>
+        <v>0.4852425019061772</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5030218666722647</v>
+        <v>0.4852369846641875</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5030155426782568</v>
+        <v>0.4852306606701796</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5030101748896784</v>
+        <v>0.4852252928816013</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5030102116381701</v>
+        <v>0.485225329630093</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5030103218836456</v>
+        <v>0.4852254398755685</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.501156825476262</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5030103953806292</v>
+        <v>0.4852255133725521</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5030105791230884</v>
+        <v>0.4852256971150113</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5030121225597448</v>
+        <v>0.4852272405516678</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5030135924994179</v>
+        <v>0.4852287104913409</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5030148419481399</v>
+        <v>0.4852299599400628</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5030162016423373</v>
+        <v>0.4852313196342601</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.503013996732828</v>
+        <v>0.4852291147247509</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5030135924994179</v>
+        <v>0.4852287104913409</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5030127472841059</v>
+        <v>0.4852278652760288</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5030132985114832</v>
+        <v>0.4852284165034061</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5030129677750569</v>
+        <v>0.4852280857669797</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.331760215741336</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5030126737871223</v>
+        <v>0.4852277917790452</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5030127472841059</v>
+        <v>0.4852278652760288</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5030123063022041</v>
+        <v>0.4852274242941269</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5030121960567285</v>
+        <v>0.4852273140486514</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.931760215741336</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5030121593082368</v>
+        <v>0.4852272773001597</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5030123063022041</v>
+        <v>0.4852274242941269</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5030118285718104</v>
+        <v>0.4852269465637333</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5030127840325976</v>
+        <v>0.4852279020245205</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5030127472841059</v>
+        <v>0.4852278652760288</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5030124165476796</v>
+        <v>0.4852275345396025</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5030128575295815</v>
+        <v>0.4852279755215044</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5030122328052204</v>
+        <v>0.4852273507971433</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5030120490627612</v>
+        <v>0.4852271670546842</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5030116448293512</v>
+        <v>0.4852267628212741</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5030107996140393</v>
+        <v>0.4852259176059621</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5030107628655476</v>
+        <v>0.4852258808574704</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5030109098595148</v>
+        <v>0.4852260278514377</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9011568254762614</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5030108363625312</v>
+        <v>0.4852259543544541</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5030109098595148</v>
+        <v>0.4852260278514377</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.134013026559911</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5030109466080067</v>
+        <v>0.4852260645999296</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5030108363625312</v>
+        <v>0.4852259543544541</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5030112773444331</v>
+        <v>0.485226395336356</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9011568254762614</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5030111670989575</v>
+        <v>0.4852262850908804</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5030111303504656</v>
+        <v>0.4852262483423885</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.503011056853482</v>
+        <v>0.4852261748454049</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5030110201049903</v>
+        <v>0.4852261380969132</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5030107996140393</v>
+        <v>0.4852259176059621</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5030107261170557</v>
+        <v>0.4852258441089785</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5030106526200721</v>
+        <v>0.4852257706119949</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.501156825476262</v>
+        <v>-1.734013026559911</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.503010689368564</v>
+        <v>0.4852258073604868</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5030105791230884</v>
+        <v>0.4852256971150113</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.503010689368564</v>
+        <v>0.4852258073604868</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.931760215741336</v>
+        <v>1.666793665939915</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5030109833564984</v>
+        <v>0.4852261013484213</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_3_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.1076354480908829</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684261</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.331760215741336</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768425</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.331760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001440624600977171</v>
+        <v>-0.00011440207466844</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1655000969062406</v>
+        <v>-0.1314260108501675</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.4313973956586085</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.501156825476262</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.01612649947684253</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.2161264994768426</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.331760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1656441593663383</v>
+        <v>-0.1315404129248359</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586085</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1657682518138685</v>
+        <v>-0.1316410907667074</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4462079236830044</v>
+        <v>0.3620145909370595</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7275048455840717</v>
+        <v>0.5930831723785309</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03179222087841815</v>
+        <v>0.02579346359715836</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.34416515618997</v>
+        <v>0.282074797496666</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05575285145953988</v>
+        <v>0.04523294677178154</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586084</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4238679552313215</v>
+        <v>0.3467386195653142</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06773313016383531</v>
+        <v>0.05495237657255951</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684264</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5035760591860627</v>
+        <v>0.4114067461484878</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0179237182952341</v>
+        <v>0.01454194069679433</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4716042187207353</v>
+        <v>0.3854674669654025</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009957424659006186</v>
+        <v>0.008077569606428478</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.331760215741336</v>
+        <v>0.4313973956586084</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4735784377646129</v>
+        <v>0.3870682251335094</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02092243924636031</v>
+        <v>0.01697463475754199</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5054782394943614</v>
+        <v>0.41294893038133</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008216978835471123</v>
+        <v>0.006665593522724251</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.500971457269542</v>
+        <v>0.4092915785630494</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005849429848778323</v>
+        <v>0.004745471362267386</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586083</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5044516383535103</v>
+        <v>0.4121141483421887</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002299341364440974</v>
+        <v>0.001864816180810384</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5031959673674898</v>
+        <v>0.4110946121483066</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001303659778791039</v>
+        <v>0.001055492258902515</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768427</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5035012441204346</v>
+        <v>0.4113412333536937</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.00049293255380905</v>
+        <v>0.0003989830153545123</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5031835784416129</v>
+        <v>0.4110824918624006</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002284036140042285</v>
+        <v>0.0001843651962675816</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5031470254295733</v>
+        <v>0.411051878381504</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.057648120152129e-05</v>
+        <v>6.44299753144418e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5030792849977775</v>
+        <v>0.4109959202976064</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.028024483792712e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.503038856734124</v>
+        <v>0.4109621142089013</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5030338366287889</v>
+        <v>0.4109570978267763</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5030298185844452</v>
+        <v>0.410952897617454</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684275</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5030273839142544</v>
+        <v>0.4109499137383483</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.6636503946122936</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5030218666722647</v>
+        <v>0.4109444699933419</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5030155426782568</v>
+        <v>0.4109384772599116</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5030101748896784</v>
+        <v>0.4109331094713332</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5030102116381701</v>
+        <v>0.4109331462198249</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5030103218836456</v>
+        <v>0.4109332564653004</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5030103953806292</v>
+        <v>0.410933329962284</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5030105791230884</v>
+        <v>0.4109335137047432</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5030121225597448</v>
+        <v>0.4109350571413997</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5030135924994179</v>
+        <v>0.4109365270810728</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5030148419481399</v>
+        <v>0.4109377765297948</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5030162016423373</v>
+        <v>0.4109391362239921</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.0161264994768428</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.503013996732828</v>
+        <v>0.4109369313144828</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5030135924994179</v>
+        <v>0.4109365270810728</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5030127472841059</v>
+        <v>0.4109356818657608</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5030132985114832</v>
+        <v>0.4109362330931381</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5030129677750569</v>
+        <v>0.4109359023567117</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.331760215741336</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5030126737871223</v>
+        <v>0.4109356083687772</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5030127472841059</v>
+        <v>0.4109356818657608</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5030123063022041</v>
+        <v>0.4109352408838589</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5030121960567285</v>
+        <v>0.4109351306383833</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5030121593082368</v>
+        <v>0.4109350938898916</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5030123063022041</v>
+        <v>0.4109352408838589</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5030118285718104</v>
+        <v>0.4109347631534652</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5030127840325976</v>
+        <v>0.4109357186142525</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.0161264994768428</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5030127472841059</v>
+        <v>0.4109356818657608</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5030124165476796</v>
+        <v>0.4109353511293344</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5030128575295815</v>
+        <v>0.4109357921112364</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5030122328052204</v>
+        <v>0.4109351673868752</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5030120490627612</v>
+        <v>0.4109349836444161</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5030116448293512</v>
+        <v>0.4109345794110061</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5030107996140393</v>
+        <v>0.4109337341956941</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.2161264994768428</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5030107628655476</v>
+        <v>0.4109336974472024</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684275</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5030109098595148</v>
+        <v>0.4109338444411696</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.0161264994768428</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5030108363625312</v>
+        <v>0.410933770944186</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684275</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5030109098595148</v>
+        <v>0.4109338444411696</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9011568254762614</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5030109466080067</v>
+        <v>0.4109338811896616</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.931760215741336</v>
+        <v>-0.01612649947684269</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5030108363625312</v>
+        <v>0.410933770944186</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.01612649947684269</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5030112773444331</v>
+        <v>0.410934211926088</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9011568254762614</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5030111670989575</v>
+        <v>0.4109341016806125</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5030111303504656</v>
+        <v>0.4109340649321205</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.503011056853482</v>
+        <v>0.4109339914351369</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5030110201049903</v>
+        <v>0.4109339546866452</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5030107996140393</v>
+        <v>0.4109337341956941</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5030107261170557</v>
+        <v>0.4109336606987105</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.8636503946122936</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5030106526200721</v>
+        <v>0.4109335872017268</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.501156825476262</v>
+        <v>-0.01612649947684275</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.503010689368564</v>
+        <v>0.4109336239502188</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.931760215741336</v>
+        <v>0.6313973956586082</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5030105791230884</v>
+        <v>0.4109335137047432</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.503010689368564</v>
+        <v>0.4109336239502188</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.931760215741336</v>
+        <v>1.278921290794059</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5030109833564984</v>
+        <v>0.4109339179381533</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_3_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.489286869764328</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.1076354480908829</v>
+        <v>0.2599999999999997</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5520305633544922</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.4313973956586084</v>
+        <v>-0.02000000000000024</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.7201764583587646</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.3853446543216705</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.01612649947684261</v>
+        <v>0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.3022332489490509</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4299311339855194</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.5148049592971802</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3834747076034546</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.48054039478302</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4159553945064545</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.3</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.5964109301567078</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4498413801193237</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5548557639122009</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4883233606815338</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.5479403138160706</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.3084525465965271</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.16</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4309178590774536</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4323209226131439</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4788081645965576</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5238147377967834</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4132493436336517</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6313973956586084</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5719718933105469</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4881860911846161</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.6462175250053406</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3832457065582275</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5579717755317688</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4621630012989044</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5778790712356567</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.5972416400909424</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.6234424114227295</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.278921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.7966629862785339</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.2484568208456039</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.6189505457878113</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.6041370034217834</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4313973956586085</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3422043323516846</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.695919394493103</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2161264994768425</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4335381090641022</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.5143142342567444</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.7037714123725891</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.16</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.5795685648918152</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.6562938690185547</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6746481657028198</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.8679262399673462</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.278921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6011567711830139</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.00011440207466844</v>
+        <v>-0.0001132297395697096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1314260108501675</v>
+        <v>-0.1300792229893992</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.02780677191913128</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.6923151612281799</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.1599656641483307</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.4576736986637115</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.2826114296913147</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5109651684761047</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3328065872192383</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4313973956586085</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.6453337073326111</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.2161264994768426</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.4371157586574554</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.16</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="55">
@@ -44662,17 +44662,17 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5370854139328003</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="56">
@@ -45457,17 +45457,17 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.4633501470088959</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.01612649947684253</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.4729794859886169</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.2161264994768426</v>
+        <v>0.3</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.6188303232192993</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1315404129248359</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.8318102359771729</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.6313973956586085</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1316410907667074</v>
+        <v>-0.1302860157581051</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3620145909370595</v>
+        <v>0.3364313446722635</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.1149341762065887</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5930831723785309</v>
+        <v>0.5432226340878866</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02579346359715836</v>
+        <v>0.0239706626721457</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.6359613537788391</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.282074797496666</v>
+        <v>0.2541929419558563</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04523294677178154</v>
+        <v>0.04203624669638161</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.7657520771026611</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6313973956586084</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3467386195653142</v>
+        <v>0.3142870300491233</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05495237657255951</v>
+        <v>0.05106938708129904</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.1850852519273758</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.01612649947684264</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4114067461484878</v>
+        <v>0.3743853010803733</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01454194069679433</v>
+        <v>0.01351423937528155</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3149859309196472</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2161264994768427</v>
+        <v>0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3854674669654025</v>
+        <v>0.3502791906641927</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008077569606428478</v>
+        <v>0.007506349013754104</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9447494745254517</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4313973956586084</v>
+        <v>0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3870682251335094</v>
+        <v>0.351766467453772</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01697463475754199</v>
+        <v>0.01577426797503244</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.5405718684196472</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.278921290794059</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.41294893038133</v>
+        <v>0.3758181862179595</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006665593522724251</v>
+        <v>0.006194485882865911</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.775592029094696</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4092915785630494</v>
+        <v>0.3724187800890964</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004745471362267386</v>
+        <v>0.004409109010908583</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.1849680244922638</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6313973956586083</v>
+        <v>0.3</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4121141483421887</v>
+        <v>0.3750416551579663</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001864816180810384</v>
+        <v>0.001733100734522361</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.6401490569114685</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4110946121483066</v>
+        <v>0.3740935859290853</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001055492258902515</v>
+        <v>0.0009815044268860604</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.163905531167984</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2161264994768427</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4113412333536937</v>
+        <v>0.3743224812434371</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003989830153545123</v>
+        <v>0.0003707981538181509</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2115387916564941</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4110824918624006</v>
+        <v>0.3740817844933211</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001843651962675816</v>
+        <v>0.0001711536709465875</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.1274401545524597</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.411051878381504</v>
+        <v>0.3740530263687507</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.44299753144418e-05</v>
+        <v>5.958602354831795e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1223665103316307</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4109959202976064</v>
+        <v>0.3740008969771571</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.551038732133709e-05</v>
+        <v>1.407943006636009e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3589250147342682</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4109621142089013</v>
+        <v>0.373969408277363</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.49368653649805e-06</v>
+        <v>4.539715033180046e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3714444041252136</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4109570978267763</v>
+        <v>0.3739643933845221</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>1.369014529177619e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.5854507088661194</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.410952897617454</v>
+        <v>0.3739601204669564</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2829963862895966</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.01612649947684275</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4109499137383483</v>
+        <v>0.3739569528453916</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.113922692835331</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6636503946122936</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4109444699933419</v>
+        <v>0.3739515835184038</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2136410176753998</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4109384772599116</v>
+        <v>0.3739455907849735</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4034865200519562</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4109331094713332</v>
+        <v>0.3739402229963951</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.3870296776294708</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4109331462198249</v>
+        <v>0.3739402597448868</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.4822294116020203</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4109332564653004</v>
+        <v>0.3739403699903623</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4393982887268066</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.2161264994768428</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.410933329962284</v>
+        <v>0.373940443487346</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.9243154525756836</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4109335137047432</v>
+        <v>0.3739406272298051</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.9435219168663025</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4109350571413997</v>
+        <v>0.3739421706664616</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.9512658715248108</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.278921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4109365270810728</v>
+        <v>0.3739436406061347</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.9793888926506042</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.278921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4109377765297948</v>
+        <v>0.3739448900548566</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.996204674243927</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4109391362239921</v>
+        <v>0.373946249749054</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.009908420033752918</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.0161264994768428</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4109369313144828</v>
+        <v>0.3739440448395447</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.03647046908736229</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4109365270810728</v>
+        <v>0.3739436406061347</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.6076506376266479</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4109356818657608</v>
+        <v>0.3739427953908227</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.1344674527645111</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4109362330931381</v>
+        <v>0.3739433466181999</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.1281605362892151</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4109359023567117</v>
+        <v>0.3739430158817735</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.5652016401290894</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4109356083687772</v>
+        <v>0.3739427218938391</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.03346553444862366</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4109356818657608</v>
+        <v>0.3739427953908227</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.4411059617996216</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.3</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4109352408838589</v>
+        <v>0.3739423544089208</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.272377073764801</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2161264994768428</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4109351306383833</v>
+        <v>0.3739422441634452</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.5180628299713135</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.2161264994768428</v>
+        <v>0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4109350938898916</v>
+        <v>0.3739422074149535</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.04046589136123657</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4109352408838589</v>
+        <v>0.3739423544089208</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.9808242321014404</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4109347631534652</v>
+        <v>0.3739418766785271</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.7467491626739502</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4109357186142525</v>
+        <v>0.3739428321393144</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.08945015072822571</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.0161264994768428</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4109356818657608</v>
+        <v>0.3739427953908227</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4272117614746094</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4109353511293344</v>
+        <v>0.3739424646543963</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.116204246878624</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4109357921112364</v>
+        <v>0.3739429056362982</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.06255731731653214</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4109351673868752</v>
+        <v>0.3739422809119371</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.1261657178401947</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4109349836444161</v>
+        <v>0.373942097169478</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.01630265451967716</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4109345794110061</v>
+        <v>0.3739416929360679</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1643736809492111</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4109337341956941</v>
+        <v>0.373940847720756</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.6112172603607178</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2161264994768428</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4109336974472024</v>
+        <v>0.3739408109722643</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.2162638902664185</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.01612649947684275</v>
+        <v>0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4109338444411696</v>
+        <v>0.3739409579662315</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.376036673784256</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.0161264994768428</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.410933770944186</v>
+        <v>0.3739408844692479</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.6854792237281799</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.01612649947684275</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4109338444411696</v>
+        <v>0.3739409579662315</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.1162773072719574</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4109338811896616</v>
+        <v>0.3739409947147234</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.8244302868843079</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.01612649947684269</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.410933770944186</v>
+        <v>0.3739408844692479</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.1657611429691315</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.01612649947684269</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.410934211926088</v>
+        <v>0.3739413254511498</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4126265048980713</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8636503946122936</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4109341016806125</v>
+        <v>0.3739412152056743</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2392496019601822</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4109340649321205</v>
+        <v>0.3739411784571824</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.2223980724811554</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4109339914351369</v>
+        <v>0.3739411049601987</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.1636876463890076</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4109339546866452</v>
+        <v>0.373941068211707</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1555505096912384</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4109337341956941</v>
+        <v>0.373940847720756</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.3368065059185028</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4109336606987105</v>
+        <v>0.3739407742237724</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3190625309944153</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8636503946122936</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4109335872017268</v>
+        <v>0.3739407007267887</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.1645626574754715</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.01612649947684275</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4109336239502188</v>
+        <v>0.3739407374752807</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.5398553609848022</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.6313973956586082</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4109335137047432</v>
+        <v>0.3739406272298051</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.7346620559692383</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.278921290794059</v>
+        <v>0.8600000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4109336239502188</v>
+        <v>0.3739407374752807</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.5636892318725586</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.278921290794059</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4109339179381533</v>
+        <v>0.3739410314632151</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_3_000008.xlsx
+++ b/out/MLP-Mamba1_repeat_3_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.489286869764328</v>
+        <v>0.4892869293689728</v>
       </c>
       <c r="JB2" t="n">
         <v>0.2599999999999997</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.5520305633544922</v>
+        <v>0.552030622959137</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.02000000000000024</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.3853446543216705</v>
+        <v>0.3853449821472168</v>
       </c>
       <c r="JB5" t="n">
         <v>0.16</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.4299311339855194</v>
+        <v>0.4299311637878418</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.8599999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.5148049592971802</v>
+        <v>0.514805018901825</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.5799999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.48054039478302</v>
+        <v>0.4805404245853424</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.3</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.4159553945064545</v>
+        <v>0.4159554243087769</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.3</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.5548557639122009</v>
+        <v>0.5548558235168457</v>
       </c>
       <c r="JB14" t="n">
         <v>0.8599999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.4883233606815338</v>
+        <v>0.4883234202861786</v>
       </c>
       <c r="JB15" t="n">
         <v>0.5799999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.5479403138160706</v>
+        <v>0.5479403734207153</v>
       </c>
       <c r="JB16" t="n">
         <v>0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.3084525465965271</v>
+        <v>0.3084525167942047</v>
       </c>
       <c r="JB17" t="n">
         <v>0.16</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4309178590774536</v>
+        <v>0.430917888879776</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.5799999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.5238147377967834</v>
+        <v>0.5238147974014282</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.4399999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.4132493436336517</v>
+        <v>0.4132493734359741</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.3</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.5719718933105469</v>
+        <v>0.5719719529151917</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.4881860911846161</v>
+        <v>0.4881861507892609</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.6462175250053406</v>
+        <v>0.6462176442146301</v>
       </c>
       <c r="JB25" t="n">
         <v>0.5799999999999998</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.3832457065582275</v>
+        <v>0.3832456767559052</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.5579717755317688</v>
+        <v>0.5579718351364136</v>
       </c>
       <c r="JB27" t="n">
         <v>0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.4621630012989044</v>
+        <v>0.462163120508194</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.5778790712356567</v>
+        <v>0.5778791904449463</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.5972416400909424</v>
+        <v>0.5972417593002319</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.6234424114227295</v>
+        <v>0.6234424710273743</v>
       </c>
       <c r="JB31" t="n">
         <v>0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.7966629862785339</v>
+        <v>0.7966631650924683</v>
       </c>
       <c r="JB32" t="n">
         <v>0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.2484568208456039</v>
+        <v>0.2484567612409592</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.6189505457878113</v>
+        <v>0.6189506053924561</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.6041370034217834</v>
+        <v>0.6041370630264282</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.695919394493103</v>
+        <v>0.6959195137023926</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.4335381090641022</v>
+        <v>0.4335381686687469</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.5143142342567444</v>
+        <v>0.5143143534660339</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.16</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.7037714123725891</v>
+        <v>0.7037715911865234</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.16</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.5795685648918152</v>
+        <v>0.5795686841011047</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.6562938690185547</v>
+        <v>0.6562939882278442</v>
       </c>
       <c r="JB42" t="n">
         <v>0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.6746481657028198</v>
+        <v>0.6746482253074646</v>
       </c>
       <c r="JB43" t="n">
         <v>0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.6011567711830139</v>
+        <v>0.6011572480201721</v>
       </c>
       <c r="JB45" t="n">
         <v>0.5799999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.02780677191913128</v>
+        <v>0.02780680917203426</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.3</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.6923151612281799</v>
+        <v>0.6923150420188904</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.5799999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.1599656641483307</v>
+        <v>0.1599656045436859</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.4576736986637115</v>
+        <v>0.4576738178730011</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.2826114296913147</v>
+        <v>0.2826114594936371</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.5109651684761047</v>
+        <v>0.5109652876853943</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.7199999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.3328065872192383</v>
+        <v>0.3328066468238831</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.7199999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.6453337073326111</v>
+        <v>0.6453338265419006</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.4399999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.4371157586574554</v>
+        <v>0.4371158480644226</v>
       </c>
       <c r="JB54" t="n">
         <v>0.16</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.5370854139328003</v>
+        <v>0.5370855331420898</v>
       </c>
       <c r="JB55" t="n">
         <v>0.1600000000000001</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.4633501470088959</v>
+        <v>0.4633502066135406</v>
       </c>
       <c r="JB56" t="n">
         <v>0.02000000000000007</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.4729794859886169</v>
+        <v>0.4729795455932617</v>
       </c>
       <c r="JB57" t="n">
         <v>0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.6188303232192993</v>
+        <v>0.6188304424285889</v>
       </c>
       <c r="JB58" t="n">
         <v>0.02000000000000007</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.8318102359771729</v>
+        <v>0.8318103551864624</v>
       </c>
       <c r="JB59" t="n">
         <v>0.3</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.1149341762065887</v>
+        <v>0.1149342060089111</v>
       </c>
       <c r="JB60" t="n">
         <v>0.5799999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.6359613537788391</v>
+        <v>0.6359614729881287</v>
       </c>
       <c r="JB61" t="n">
         <v>0.4399999999999999</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.7657520771026611</v>
+        <v>0.7657522559165955</v>
       </c>
       <c r="JB62" t="n">
         <v>0.1600000000000001</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.1850852519273758</v>
+        <v>0.1850854456424713</v>
       </c>
       <c r="JB63" t="n">
         <v>0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3149859309196472</v>
+        <v>0.314985990524292</v>
       </c>
       <c r="JB64" t="n">
         <v>0.3</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.9447494745254517</v>
+        <v>0.9447495341300964</v>
       </c>
       <c r="JB65" t="n">
         <v>0.3</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.5405718684196472</v>
+        <v>0.5405725240707397</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.3</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.775592029094696</v>
+        <v>0.7755923271179199</v>
       </c>
       <c r="JB67" t="n">
         <v>0.5799999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.1849680244922638</v>
+        <v>0.1849681735038757</v>
       </c>
       <c r="JB68" t="n">
         <v>0.3</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.6401490569114685</v>
+        <v>0.6401493549346924</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.163905531167984</v>
+        <v>0.1639056801795959</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.7199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.2115387916564941</v>
+        <v>0.2115388512611389</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1274401545524597</v>
+        <v>0.1274401843547821</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1223665103316307</v>
+        <v>0.1223665699362755</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.3589250147342682</v>
+        <v>0.358925074338913</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.3714444041252136</v>
+        <v>0.3714444637298584</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.2829963862895966</v>
+        <v>0.2829964160919189</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.113922692835331</v>
+        <v>0.1139227151870728</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.1199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.2136410176753998</v>
+        <v>0.2136410623788834</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.9999999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.4034865200519562</v>
+        <v>0.4034865498542786</v>
       </c>
       <c r="JB80" t="n">
         <v>-0.7199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.3870296776294708</v>
+        <v>0.3870297074317932</v>
       </c>
       <c r="JB81" t="n">
         <v>0.16</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.4822294116020203</v>
+        <v>0.4822295010089874</v>
       </c>
       <c r="JB82" t="n">
         <v>0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.9435219168663025</v>
+        <v>0.943522036075592</v>
       </c>
       <c r="JB85" t="n">
         <v>0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.009908420033752918</v>
+        <v>0.009908485226333141</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.03647046908736229</v>
+        <v>0.03647082671523094</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.5799999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.6076506376266479</v>
+        <v>0.6076515913009644</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.8599999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.1344674527645111</v>
+        <v>0.1344677954912186</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.5799999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.1281605362892151</v>
+        <v>0.1281608194112778</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.5799999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.5652016401290894</v>
+        <v>0.5652021169662476</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.5799999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.03346553444862366</v>
+        <v>0.03346561640501022</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.5799999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.4411059617996216</v>
+        <v>0.4411062598228455</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.272377073764801</v>
+        <v>0.2723773121833801</v>
       </c>
       <c r="JB97" t="n">
         <v>0.02000000000000007</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.5180628299713135</v>
+        <v>0.5180630683898926</v>
       </c>
       <c r="JB98" t="n">
         <v>0.3</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.04046589136123657</v>
+        <v>0.04046593606472015</v>
       </c>
       <c r="JB99" t="n">
         <v>0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.9808242321014404</v>
+        <v>0.98082435131073</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.7467491626739502</v>
+        <v>0.7467503547668457</v>
       </c>
       <c r="JB101" t="n">
         <v>0.1600000000000001</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.08945015072822571</v>
+        <v>0.0894504114985466</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.4272117614746094</v>
+        <v>0.4272122383117676</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.116204246878624</v>
+        <v>0.1162044778466225</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.06255731731653214</v>
+        <v>0.06255744397640228</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.1261657178401947</v>
+        <v>0.1261658817529678</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.01630265451967716</v>
+        <v>0.01630270108580589</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.7199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.1643736809492111</v>
+        <v>0.1643738299608231</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.6112172603607178</v>
+        <v>0.6112173199653625</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.2162638902664185</v>
+        <v>0.2162640690803528</v>
       </c>
       <c r="JB110" t="n">
         <v>0.16</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.376036673784256</v>
+        <v>0.3760368525981903</v>
       </c>
       <c r="JB111" t="n">
         <v>0.16</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.6854792237281799</v>
+        <v>0.6854795813560486</v>
       </c>
       <c r="JB112" t="n">
         <v>0.1600000000000001</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.1162773072719574</v>
+        <v>0.1162774115800858</v>
       </c>
       <c r="JB113" t="n">
         <v>0.16</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.8244302868843079</v>
+        <v>0.8244304656982422</v>
       </c>
       <c r="JB114" t="n">
         <v>0.4399999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.1657611429691315</v>
+        <v>0.1657611876726151</v>
       </c>
       <c r="JB115" t="n">
         <v>0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4126265048980713</v>
+        <v>0.4126266539096832</v>
       </c>
       <c r="JB116" t="n">
         <v>0.1600000000000001</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2392496019601822</v>
+        <v>0.239249661564827</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.2223980724811554</v>
+        <v>0.222398117184639</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.1636876463890076</v>
+        <v>0.16368767619133</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.8599999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.1555505096912384</v>
+        <v>0.1555505692958832</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.3368065059185028</v>
+        <v>0.3368065655231476</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.7199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3190625309944153</v>
+        <v>0.3190625607967377</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.1645626574754715</v>
+        <v>0.1645627319812775</v>
       </c>
       <c r="JB123" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.7346620559692383</v>
+        <v>0.7346622347831726</v>
       </c>
       <c r="JB125" t="n">
         <v>0.8600000000000003</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.5636892318725586</v>
+        <v>0.5636895298957825</v>
       </c>
       <c r="JB126" t="n">
         <v>1.14</v>
